--- a/Team-Data/2014-15/2-5-2014-15.xlsx
+++ b/Team-Data/2014-15/2-5-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>6.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -760,7 +827,7 @@
         <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL2" t="n">
         <v>5</v>
@@ -772,10 +839,10 @@
         <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
         <v>9</v>
@@ -814,7 +881,7 @@
         <v>6</v>
       </c>
       <c r="BC2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
         <v>22</v>
@@ -951,13 +1018,13 @@
         <v>13</v>
       </c>
       <c r="AN3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
         <v>28</v>
       </c>
       <c r="AP3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ3" t="n">
         <v>17</v>
@@ -984,7 +1051,7 @@
         <v>27</v>
       </c>
       <c r="AY3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ3" t="n">
         <v>18</v>
@@ -993,7 +1060,7 @@
         <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
         <v>17</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
@@ -1115,7 +1182,7 @@
         <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
         <v>23</v>
@@ -1127,7 +1194,7 @@
         <v>18</v>
       </c>
       <c r="AL4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM4" t="n">
         <v>18</v>
@@ -1142,7 +1209,7 @@
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
@@ -1157,7 +1224,7 @@
         <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
         <v>20</v>
@@ -1175,7 +1242,7 @@
         <v>20</v>
       </c>
       <c r="BB4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
         <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>0.449</v>
+        <v>0.438</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J5" t="n">
-        <v>84.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K5" t="n">
         <v>0.424</v>
@@ -1234,58 +1301,58 @@
         <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.303</v>
+        <v>0.305</v>
       </c>
       <c r="O5" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P5" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.732</v>
+        <v>0.73</v>
       </c>
       <c r="R5" t="n">
         <v>10.3</v>
       </c>
       <c r="S5" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T5" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="U5" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V5" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="W5" t="n">
         <v>5.8</v>
       </c>
       <c r="X5" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Y5" t="n">
         <v>5.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.7</v>
+        <v>94.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1303,7 +1370,7 @@
         <v>27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK5" t="n">
         <v>29</v>
@@ -1318,13 +1385,13 @@
         <v>30</v>
       </c>
       <c r="AO5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AP5" t="n">
         <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR5" t="n">
         <v>21</v>
@@ -1333,7 +1400,7 @@
         <v>6</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
         <v>26</v>
@@ -1345,7 +1412,7 @@
         <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
         <v>22</v>
@@ -1354,7 +1421,7 @@
         <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
         <v>27</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -1467,22 +1534,22 @@
         <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
         <v>11</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
         <v>4</v>
       </c>
       <c r="AI6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ6" t="n">
         <v>17</v>
@@ -1509,10 +1576,10 @@
         <v>4</v>
       </c>
       <c r="AR6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
         <v>2</v>
@@ -1530,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1638,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>0.608</v>
+        <v>0.6</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J7" t="n">
-        <v>82</v>
+        <v>82.2</v>
       </c>
       <c r="K7" t="n">
         <v>0.453</v>
@@ -1598,28 +1665,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="O7" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="P7" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.756</v>
+        <v>0.754</v>
       </c>
       <c r="R7" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S7" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="T7" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U7" t="n">
         <v>21.5</v>
@@ -1634,43 +1701,43 @@
         <v>4.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB7" t="n">
         <v>101.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
         <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL7" t="n">
         <v>9</v>
@@ -1682,22 +1749,22 @@
         <v>13</v>
       </c>
       <c r="AO7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR7" t="n">
         <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU7" t="n">
         <v>14</v>
@@ -1718,7 +1785,7 @@
         <v>2</v>
       </c>
       <c r="BA7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -1756,13 +1823,13 @@
         <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>0.667</v>
+        <v>0.647</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,40 +1838,40 @@
         <v>40.3</v>
       </c>
       <c r="J8" t="n">
-        <v>86</v>
+        <v>85.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0.469</v>
+        <v>0.47</v>
       </c>
       <c r="L8" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="M8" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O8" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="P8" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="R8" t="n">
         <v>10.6</v>
       </c>
       <c r="S8" t="n">
-        <v>31.6</v>
+        <v>31.3</v>
       </c>
       <c r="T8" t="n">
-        <v>42.3</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="V8" t="n">
         <v>12.3</v>
@@ -1813,13 +1880,13 @@
         <v>8.1</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA8" t="n">
         <v>21.9</v>
@@ -1828,19 +1895,19 @@
         <v>106.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
         <v>14</v>
@@ -1849,34 +1916,34 @@
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
         <v>20</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ8" t="n">
         <v>13</v>
       </c>
       <c r="AR8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT8" t="n">
         <v>20</v>
@@ -1891,10 +1958,10 @@
         <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ8" t="n">
         <v>13</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -2013,13 +2080,13 @@
         <v>-3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>20</v>
       </c>
       <c r="AF9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG9" t="n">
         <v>20</v>
@@ -2028,7 +2095,7 @@
         <v>17</v>
       </c>
       <c r="AI9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ9" t="n">
         <v>3</v>
@@ -2046,16 +2113,16 @@
         <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP9" t="n">
         <v>4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS9" t="n">
         <v>10</v>
@@ -2070,7 +2137,7 @@
         <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX9" t="n">
         <v>15</v>
@@ -2088,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>-1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
         <v>20</v>
@@ -2213,7 +2280,7 @@
         <v>22</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
         <v>28</v>
@@ -2228,7 +2295,7 @@
         <v>15</v>
       </c>
       <c r="AO10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP10" t="n">
         <v>16</v>
@@ -2246,7 +2313,7 @@
         <v>4</v>
       </c>
       <c r="AU10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV10" t="n">
         <v>8</v>
@@ -2255,10 +2322,10 @@
         <v>12</v>
       </c>
       <c r="AX10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY10" t="n">
         <v>17</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>18</v>
       </c>
       <c r="AZ10" t="n">
         <v>7</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>11.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2410,10 +2477,10 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ11" t="n">
         <v>7</v>
@@ -2422,7 +2489,7 @@
         <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" t="n">
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J12" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
@@ -2508,34 +2575,34 @@
         <v>11.7</v>
       </c>
       <c r="M12" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O12" t="n">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
       <c r="P12" t="n">
-        <v>23.9</v>
+        <v>24.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.721</v>
+        <v>0.719</v>
       </c>
       <c r="R12" t="n">
         <v>12</v>
       </c>
       <c r="S12" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T12" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U12" t="n">
         <v>21.2</v>
       </c>
       <c r="V12" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="W12" t="n">
         <v>9.800000000000001</v>
@@ -2544,25 +2611,25 @@
         <v>4.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.5</v>
+        <v>102.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>4</v>
@@ -2574,7 +2641,7 @@
         <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="n">
         <v>14</v>
@@ -2592,19 +2659,19 @@
         <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT12" t="n">
         <v>14</v>
@@ -2619,22 +2686,22 @@
         <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC12" t="n">
         <v>8</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>22</v>
@@ -2750,7 +2817,7 @@
         <v>24</v>
       </c>
       <c r="AG13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH13" t="n">
         <v>17</v>
@@ -2771,10 +2838,10 @@
         <v>19</v>
       </c>
       <c r="AN13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO13" t="n">
         <v>24</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>23</v>
       </c>
       <c r="AP13" t="n">
         <v>25</v>
@@ -2810,7 +2877,7 @@
         <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E14" t="n">
         <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.66</v>
+        <v>0.673</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2863,31 +2930,31 @@
         <v>39.2</v>
       </c>
       <c r="J14" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="M14" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.376</v>
+        <v>0.379</v>
       </c>
       <c r="O14" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P14" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="R14" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S14" t="n">
         <v>32.4</v>
@@ -2905,34 +2972,34 @@
         <v>7.7</v>
       </c>
       <c r="X14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y14" t="n">
         <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA14" t="n">
         <v>21.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.5</v>
+        <v>106.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -2953,16 +3020,16 @@
         <v>6</v>
       </c>
       <c r="AN14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP14" t="n">
         <v>5</v>
       </c>
-      <c r="AO14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>6</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR14" t="n">
         <v>27</v>
@@ -2983,7 +3050,7 @@
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -2998,7 +3065,7 @@
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E15" t="n">
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G15" t="n">
-        <v>0.271</v>
+        <v>0.265</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="J15" t="n">
-        <v>85.7</v>
+        <v>85.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.436</v>
+        <v>0.434</v>
       </c>
       <c r="L15" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M15" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="N15" t="n">
         <v>0.347</v>
       </c>
       <c r="O15" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="P15" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.746</v>
+        <v>0.748</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="T15" t="n">
-        <v>43.7</v>
+        <v>43.5</v>
       </c>
       <c r="U15" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V15" t="n">
         <v>13.2</v>
@@ -3093,19 +3160,19 @@
         <v>4.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.5</v>
+        <v>-6.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,10 +3184,10 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="n">
         <v>8</v>
@@ -3129,7 +3196,7 @@
         <v>25</v>
       </c>
       <c r="AL15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM15" t="n">
         <v>23</v>
@@ -3138,25 +3205,25 @@
         <v>18</v>
       </c>
       <c r="AO15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR15" t="n">
         <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV15" t="n">
         <v>7</v>
@@ -3171,10 +3238,10 @@
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB15" t="n">
         <v>18</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>5.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3299,7 +3366,7 @@
         <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>7</v>
@@ -3308,7 +3375,7 @@
         <v>16</v>
       </c>
       <c r="AK16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>28</v>
@@ -3320,7 +3387,7 @@
         <v>16</v>
       </c>
       <c r="AO16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP16" t="n">
         <v>11</v>
@@ -3329,7 +3396,7 @@
         <v>6</v>
       </c>
       <c r="AR16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS16" t="n">
         <v>12</v>
@@ -3341,7 +3408,7 @@
         <v>9</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW16" t="n">
         <v>8</v>
@@ -3362,7 +3429,7 @@
         <v>11</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>-3.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF17" t="n">
         <v>18</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
@@ -3502,7 +3569,7 @@
         <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>13</v>
@@ -3532,19 +3599,19 @@
         <v>23</v>
       </c>
       <c r="AY17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ17" t="n">
         <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>29</v>
       </c>
       <c r="BC17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
@@ -3660,10 +3727,10 @@
         <v>13</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI18" t="n">
         <v>13</v>
@@ -3696,7 +3763,7 @@
         <v>24</v>
       </c>
       <c r="AS18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT18" t="n">
         <v>25</v>
@@ -3717,7 +3784,7 @@
         <v>11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA18" t="n">
         <v>21</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
         <v>30</v>
@@ -3845,10 +3912,10 @@
         <v>30</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ19" t="n">
         <v>12</v>
@@ -3869,10 +3936,10 @@
         <v>4</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR19" t="n">
         <v>5</v>
@@ -3887,7 +3954,7 @@
         <v>11</v>
       </c>
       <c r="AV19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" t="n">
         <v>23</v>
       </c>
       <c r="G20" t="n">
-        <v>0.521</v>
+        <v>0.531</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J20" t="n">
-        <v>83.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L20" t="n">
         <v>6.6</v>
@@ -3967,61 +4034,61 @@
         <v>19.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="O20" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P20" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.768</v>
+        <v>0.76</v>
       </c>
       <c r="R20" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="S20" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T20" t="n">
-        <v>44.1</v>
+        <v>44.4</v>
       </c>
       <c r="U20" t="n">
         <v>21.4</v>
       </c>
       <c r="V20" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W20" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X20" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="Y20" t="n">
         <v>6</v>
       </c>
       <c r="Z20" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="AA20" t="n">
         <v>18.9</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
         <v>100.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>15</v>
       </c>
       <c r="AF20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG20" t="n">
         <v>15</v>
@@ -4036,7 +4103,7 @@
         <v>13</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
@@ -4051,37 +4118,37 @@
         <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AS20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>23</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY20" t="n">
         <v>29</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-7.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
         <v>29</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
         <v>29</v>
@@ -4254,13 +4321,13 @@
         <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX21" t="n">
         <v>27</v>
       </c>
       <c r="AY21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -4379,10 +4446,10 @@
         <v>1.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF22" t="n">
         <v>16</v>
@@ -4391,13 +4458,13 @@
         <v>16</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK22" t="n">
         <v>21</v>
@@ -4406,7 +4473,7 @@
         <v>17</v>
       </c>
       <c r="AM22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN22" t="n">
         <v>27</v>
@@ -4421,7 +4488,7 @@
         <v>20</v>
       </c>
       <c r="AR22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
@@ -4445,7 +4512,7 @@
         <v>12</v>
       </c>
       <c r="AZ22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E23" t="n">
         <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>0.294</v>
+        <v>0.288</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J23" t="n">
         <v>81.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N23" t="n">
         <v>0.362</v>
@@ -4519,46 +4586,46 @@
         <v>14.4</v>
       </c>
       <c r="P23" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.731</v>
+        <v>0.732</v>
       </c>
       <c r="R23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>40.4</v>
+        <v>40.7</v>
       </c>
       <c r="U23" t="n">
         <v>20.5</v>
       </c>
       <c r="V23" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W23" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X23" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA23" t="n">
         <v>18.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.2</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.2</v>
+        <v>-6.4</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4573,16 +4640,16 @@
         <v>26</v>
       </c>
       <c r="AH23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ23" t="n">
         <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
         <v>20</v>
@@ -4600,31 +4667,31 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR23" t="n">
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
       </c>
       <c r="AU23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX23" t="n">
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
         <v>20</v>
@@ -4633,7 +4700,7 @@
         <v>28</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4779,7 +4846,7 @@
         <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
@@ -4806,13 +4873,13 @@
         <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -4847,46 +4914,46 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E25" t="n">
         <v>28</v>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G25" t="n">
-        <v>0.549</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="J25" t="n">
         <v>86.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L25" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="M25" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O25" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P25" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.786</v>
+        <v>0.787</v>
       </c>
       <c r="R25" t="n">
         <v>10.6</v>
@@ -4916,28 +4983,28 @@
         <v>22.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>106.3</v>
+        <v>106.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
       </c>
       <c r="AF25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI25" t="n">
         <v>3</v>
@@ -4946,19 +5013,19 @@
         <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP25" t="n">
         <v>24</v>
@@ -4967,40 +5034,40 @@
         <v>2</v>
       </c>
       <c r="AR25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
         <v>19</v>
       </c>
       <c r="AT25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU25" t="n">
         <v>21</v>
       </c>
       <c r="AV25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW25" t="n">
         <v>5</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ25" t="n">
         <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
       </c>
       <c r="BC25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E26" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F26" t="n">
         <v>16</v>
       </c>
       <c r="G26" t="n">
-        <v>0.68</v>
+        <v>0.673</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
@@ -5047,7 +5114,7 @@
         <v>38.4</v>
       </c>
       <c r="J26" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="K26" t="n">
         <v>0.444</v>
@@ -5056,28 +5123,28 @@
         <v>10.1</v>
       </c>
       <c r="M26" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="O26" t="n">
         <v>15.6</v>
       </c>
       <c r="P26" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="R26" t="n">
         <v>10.9</v>
       </c>
       <c r="S26" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="T26" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="U26" t="n">
         <v>22.3</v>
@@ -5092,25 +5159,25 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA26" t="n">
         <v>19.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.5</v>
+        <v>102.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AD26" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF26" t="n">
         <v>5</v>
@@ -5125,7 +5192,7 @@
         <v>9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK26" t="n">
         <v>19</v>
@@ -5143,22 +5210,22 @@
         <v>27</v>
       </c>
       <c r="AP26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT26" t="n">
         <v>3</v>
       </c>
       <c r="AU26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV26" t="n">
         <v>9</v>
@@ -5170,7 +5237,7 @@
         <v>9</v>
       </c>
       <c r="AY26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
         <v>8</v>
@@ -5179,10 +5246,10 @@
         <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -5211,67 +5278,67 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E27" t="n">
         <v>17</v>
       </c>
       <c r="F27" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" t="n">
-        <v>0.354</v>
+        <v>0.362</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
       </c>
       <c r="I27" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J27" t="n">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="K27" t="n">
-        <v>0.452</v>
+        <v>0.454</v>
       </c>
       <c r="L27" t="n">
         <v>5.2</v>
       </c>
       <c r="M27" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0.327</v>
+        <v>0.332</v>
       </c>
       <c r="O27" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="P27" t="n">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0.782</v>
       </c>
       <c r="R27" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S27" t="n">
-        <v>33.8</v>
+        <v>33.6</v>
       </c>
       <c r="T27" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U27" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="V27" t="n">
         <v>16.5</v>
       </c>
       <c r="W27" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="X27" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y27" t="n">
         <v>6</v>
@@ -5280,25 +5347,25 @@
         <v>21.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.8</v>
+        <v>101.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>-3.8</v>
+        <v>-3.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH27" t="n">
         <v>5</v>
@@ -5310,16 +5377,16 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
       </c>
       <c r="AM27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5331,10 +5398,10 @@
         <v>3</v>
       </c>
       <c r="AR27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT27" t="n">
         <v>8</v>
@@ -5361,10 +5428,10 @@
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E28" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F28" t="n">
         <v>18</v>
       </c>
       <c r="G28" t="n">
-        <v>0.625</v>
+        <v>0.633</v>
       </c>
       <c r="H28" t="n">
         <v>48.9</v>
@@ -5411,49 +5478,49 @@
         <v>37.9</v>
       </c>
       <c r="J28" t="n">
-        <v>83.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.366</v>
+        <v>0.37</v>
       </c>
       <c r="O28" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P28" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="T28" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W28" t="n">
         <v>7.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.8</v>
@@ -5468,16 +5535,16 @@
         <v>101.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG28" t="n">
         <v>9</v>
@@ -5492,25 +5559,25 @@
         <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
       </c>
       <c r="AM28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN28" t="n">
         <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
@@ -5519,19 +5586,19 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
         <v>14</v>
       </c>
       <c r="AX28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY28" t="n">
         <v>15</v>
@@ -5540,13 +5607,13 @@
         <v>9</v>
       </c>
       <c r="BA28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>4.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG29" t="n">
         <v>7</v>
@@ -5710,7 +5777,7 @@
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX29" t="n">
         <v>20</v>
@@ -5722,7 +5789,7 @@
         <v>23</v>
       </c>
       <c r="BA29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB29" t="n">
         <v>5</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
         <v>24</v>
@@ -5868,13 +5935,13 @@
         <v>20</v>
       </c>
       <c r="AO30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP30" t="n">
         <v>15</v>
       </c>
       <c r="AQ30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR30" t="n">
         <v>8</v>
@@ -5886,7 +5953,7 @@
         <v>17</v>
       </c>
       <c r="AU30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV30" t="n">
         <v>26</v>
@@ -5895,13 +5962,13 @@
         <v>26</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
         <v>14</v>
       </c>
       <c r="AZ30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA30" t="n">
         <v>24</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
@@ -5939,43 +6006,43 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E31" t="n">
         <v>31</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G31" t="n">
-        <v>0.608</v>
+        <v>0.62</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="J31" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.471</v>
+        <v>0.472</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="N31" t="n">
-        <v>0.379</v>
+        <v>0.377</v>
       </c>
       <c r="O31" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P31" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q31" t="n">
         <v>0.742</v>
@@ -5984,40 +6051,40 @@
         <v>10.3</v>
       </c>
       <c r="S31" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="T31" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="U31" t="n">
         <v>24.3</v>
       </c>
       <c r="V31" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W31" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X31" t="n">
         <v>4.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA31" t="n">
         <v>20.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
         <v>9</v>
@@ -6029,34 +6096,34 @@
         <v>10</v>
       </c>
       <c r="AH31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
       </c>
       <c r="AJ31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL31" t="n">
         <v>26</v>
       </c>
       <c r="AM31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR31" t="n">
         <v>23</v>
@@ -6065,34 +6132,34 @@
         <v>9</v>
       </c>
       <c r="AT31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AU31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV31" t="n">
         <v>20</v>
       </c>
       <c r="AW31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX31" t="n">
         <v>14</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB31" t="n">
         <v>17</v>
       </c>
       <c r="BC31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-5-2014-15</t>
+          <t>2015-02-05</t>
         </is>
       </c>
     </row>
